--- a/corpus/C03.xlsx
+++ b/corpus/C03.xlsx
@@ -747,81 +747,80 @@
         <f>F9</f>
         <v>9375.0</v>
       </c>
-      <c r="H5">
-        <f>G9</f>
-        <v>10014.0</v>
+      <c r="H5" t="n">
+        <v>7200</v>
       </c>
       <c r="I5">
         <f>H9</f>
-        <v>10697.0</v>
+        <v>7692.0</v>
       </c>
       <c r="J5">
         <f>I9</f>
-        <v>11427.0</v>
+        <v>8217.0</v>
       </c>
       <c r="K5">
         <f>J9</f>
-        <v>12206.0</v>
+        <v>8777.0</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>13039.0</v>
+        <v>9375.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>13929.0</v>
+        <v>10014.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>14879.0</v>
+        <v>10697.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>15893.0</v>
+        <v>11427.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>16977.0</v>
+        <v>12206.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>18135.0</v>
+        <v>13039.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>19372.0</v>
+        <v>13929.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>20693.0</v>
+        <v>14879.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>22104.0</v>
+        <v>15893.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>23612.0</v>
+        <v>16977.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>25223.0</v>
+        <v>18135.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>26943.0</v>
+        <v>19372.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>28781.0</v>
+        <v>20693.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>30743.0</v>
+        <v>22104.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>32839.0</v>
+        <v>23612.0</v>
       </c>
     </row>
     <row r="6">
@@ -852,79 +851,79 @@
       </c>
       <c r="H6">
         <f>ROUND(H5*Assumptions!$B$5,0)</f>
-        <v>842.0</v>
+        <v>606.0</v>
       </c>
       <c r="I6">
         <f>ROUND(I5*Assumptions!$B$5,0)</f>
-        <v>900.0</v>
+        <v>647.0</v>
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$5,0)</f>
-        <v>961.0</v>
+        <v>691.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>1027.0</v>
+        <v>738.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>1097.0</v>
+        <v>788.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>1171.0</v>
+        <v>842.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>1251.0</v>
+        <v>900.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>1337.0</v>
+        <v>961.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>1428.0</v>
+        <v>1027.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>1525.0</v>
+        <v>1097.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>1629.0</v>
+        <v>1171.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>1740.0</v>
+        <v>1251.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>1859.0</v>
+        <v>1337.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>1986.0</v>
+        <v>1428.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>2121.0</v>
+        <v>1525.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>2266.0</v>
+        <v>1629.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>2420.0</v>
+        <v>1740.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>2585.0</v>
+        <v>1859.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>2762.0</v>
+        <v>1986.0</v>
       </c>
     </row>
     <row r="7">
@@ -955,79 +954,79 @@
       </c>
       <c r="H7">
         <f>-ROUND(H5*Assumptions!$B$6,0)</f>
-        <v>-159.0</v>
+        <v>-114.0</v>
       </c>
       <c r="I7">
         <f>-ROUND(I5*Assumptions!$B$6,0)</f>
-        <v>-170.0</v>
+        <v>-122.0</v>
       </c>
       <c r="J7">
         <f>-ROUND(J5*Assumptions!$B$6,0)</f>
-        <v>-182.0</v>
+        <v>-131.0</v>
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-194.0</v>
+        <v>-140.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-207.0</v>
+        <v>-149.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-221.0</v>
+        <v>-159.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-237.0</v>
+        <v>-170.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-253.0</v>
+        <v>-182.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-270.0</v>
+        <v>-194.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-288.0</v>
+        <v>-207.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-308.0</v>
+        <v>-221.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-329.0</v>
+        <v>-237.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-351.0</v>
+        <v>-253.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-375.0</v>
+        <v>-270.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-401.0</v>
+        <v>-288.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-428.0</v>
+        <v>-308.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-458.0</v>
+        <v>-329.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-489.0</v>
+        <v>-351.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-522.0</v>
+        <v>-375.0</v>
       </c>
     </row>
     <row r="9">
@@ -1058,79 +1057,79 @@
       </c>
       <c r="H9">
         <f>H5+H6+H7</f>
-        <v>10697.0</v>
+        <v>7692.0</v>
       </c>
       <c r="I9">
         <f>I5+I6+I7</f>
-        <v>11427.0</v>
+        <v>8217.0</v>
       </c>
       <c r="J9">
         <f>J5+J6+J7</f>
-        <v>12206.0</v>
+        <v>8777.0</v>
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>13039.0</v>
+        <v>9375.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>13929.0</v>
+        <v>10014.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>14879.0</v>
+        <v>10697.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>15893.0</v>
+        <v>11427.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>16977.0</v>
+        <v>12206.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>18135.0</v>
+        <v>13039.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>19372.0</v>
+        <v>13929.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>20693.0</v>
+        <v>14879.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>22104.0</v>
+        <v>15893.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>23612.0</v>
+        <v>16977.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>25223.0</v>
+        <v>18135.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>26943.0</v>
+        <v>19372.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>28781.0</v>
+        <v>20693.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>30743.0</v>
+        <v>22104.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>32839.0</v>
+        <v>23612.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>35079.0</v>
+        <v>25223.0</v>
       </c>
     </row>
     <row r="11">
@@ -1264,79 +1263,79 @@
       </c>
       <c r="H13">
         <f>ROUND((H5+H9)/2,0)</f>
-        <v>10356.0</v>
+        <v>7446.0</v>
       </c>
       <c r="I13">
         <f>ROUND((I5+I9)/2,0)</f>
-        <v>11062.0</v>
+        <v>7955.0</v>
       </c>
       <c r="J13">
         <f>ROUND((J5+J9)/2,0)</f>
-        <v>11817.0</v>
+        <v>8497.0</v>
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>12623.0</v>
+        <v>9076.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>13484.0</v>
+        <v>9695.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>14404.0</v>
+        <v>10356.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>15386.0</v>
+        <v>11062.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>16435.0</v>
+        <v>11817.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>17556.0</v>
+        <v>12623.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>18754.0</v>
+        <v>13484.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>20033.0</v>
+        <v>14404.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>21399.0</v>
+        <v>15386.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>22858.0</v>
+        <v>16435.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>24418.0</v>
+        <v>17556.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>26083.0</v>
+        <v>18754.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>27862.0</v>
+        <v>20033.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>29762.0</v>
+        <v>21399.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>31791.0</v>
+        <v>22858.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>33959.0</v>
+        <v>24418.0</v>
       </c>
     </row>
     <row r="15">
@@ -1367,79 +1366,79 @@
       </c>
       <c r="H15">
         <f>ROUND(H13*H11,0)</f>
-        <v>1279484.0</v>
+        <v>919953.0</v>
       </c>
       <c r="I15">
         <f>ROUND(I13*I11,0)</f>
-        <v>1376777.0</v>
+        <v>990079.0</v>
       </c>
       <c r="J15">
         <f>ROUND(J13*J11,0)</f>
-        <v>1481615.0</v>
+        <v>1065354.0</v>
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>1594411.0</v>
+        <v>1146390.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>1715704.0</v>
+        <v>1233592.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>1846305.0</v>
+        <v>1327432.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>1986794.0</v>
+        <v>1428436.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>2138029.0</v>
+        <v>1537274.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>2300714.0</v>
+        <v>1654244.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>2475903.0</v>
+        <v>1780158.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>2664389.0</v>
+        <v>1915732.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>2867038.0</v>
+        <v>2061416.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>3085144.0</v>
+        <v>2218232.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>3320115.0</v>
+        <v>2387089.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>3572849.0</v>
+        <v>2568923.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>3844677.0</v>
+        <v>2764354.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>4137216.0</v>
+        <v>2974675.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>4452012.0</v>
+        <v>3201034.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>4790936.0</v>
+        <v>3444891.0</v>
       </c>
     </row>
     <row r="17">
@@ -1470,79 +1469,79 @@
       </c>
       <c r="H17">
         <f>G17+H15</f>
-        <v>6441205.0</v>
+        <v>6081674.0</v>
       </c>
       <c r="I17">
         <f>H17+I15</f>
-        <v>7817982.0</v>
+        <v>7071753.0</v>
       </c>
       <c r="J17">
         <f>I17+J15</f>
-        <v>9299597.0</v>
+        <v>8137107.0</v>
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>10894008.0</v>
+        <v>9283497.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>12609712.0</v>
+        <v>10517089.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>14456017.0</v>
+        <v>11844521.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>16442811.0</v>
+        <v>13272957.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>18580840.0</v>
+        <v>14810231.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>20881554.0</v>
+        <v>16464475.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>23357457.0</v>
+        <v>18244633.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>26021846.0</v>
+        <v>20160365.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>28888884.0</v>
+        <v>22221781.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>31974028.0</v>
+        <v>24440013.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>35294143.0</v>
+        <v>26827102.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>38866992.0</v>
+        <v>29396025.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>42711669.0</v>
+        <v>32160379.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>46848885.0</v>
+        <v>35135054.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>51300897.0</v>
+        <v>38336088.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>56091833.0</v>
+        <v>41780979.0</v>
       </c>
     </row>
   </sheetData>
@@ -2109,79 +2108,79 @@
       </c>
       <c r="H10">
         <f>ROUND(Revenue!H15*Assumptions!$B$11,0)</f>
-        <v>286732.0</v>
+        <v>206161.0</v>
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>308536.0</v>
+        <v>221877.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>332030.0</v>
+        <v>238746.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>357308.0</v>
+        <v>256906.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>384489.0</v>
+        <v>276448.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>413757.0</v>
+        <v>297478.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>445241.0</v>
+        <v>320113.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>479132.0</v>
+        <v>344503.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>515590.0</v>
+        <v>370716.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>554850.0</v>
+        <v>398933.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>597090.0</v>
+        <v>429316.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>642503.0</v>
+        <v>461963.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>691381.0</v>
+        <v>497106.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>744038.0</v>
+        <v>534947.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>800675.0</v>
+        <v>575696.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>861592.0</v>
+        <v>619492.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>927150.0</v>
+        <v>666625.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>997696.0</v>
+        <v>717352.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>1073649.0</v>
+        <v>772000.0</v>
       </c>
     </row>
     <row r="11">
@@ -2212,79 +2211,79 @@
       </c>
       <c r="H11">
         <f>ROUND(Revenue!H15*Assumptions!$B$16,0)</f>
-        <v>133706.0</v>
+        <v>96135.0</v>
       </c>
       <c r="I11">
         <f>ROUND(Revenue!I15*Assumptions!$B$16,0)</f>
-        <v>143873.0</v>
+        <v>103463.0</v>
       </c>
       <c r="J11">
         <f>ROUND(Revenue!J15*Assumptions!$B$16,0)</f>
-        <v>154829.0</v>
+        <v>111329.0</v>
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>166616.0</v>
+        <v>119798.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>179291.0</v>
+        <v>128910.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>192939.0</v>
+        <v>138717.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>207620.0</v>
+        <v>149272.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>223424.0</v>
+        <v>160645.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>240425.0</v>
+        <v>172868.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>258732.0</v>
+        <v>186027.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>278429.0</v>
+        <v>200194.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>299605.0</v>
+        <v>215418.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>322398.0</v>
+        <v>231805.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>346952.0</v>
+        <v>249451.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>373363.0</v>
+        <v>268452.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>401769.0</v>
+        <v>288875.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>432339.0</v>
+        <v>310854.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>465235.0</v>
+        <v>334508.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>500653.0</v>
+        <v>359991.0</v>
       </c>
     </row>
     <row r="12">
@@ -2418,79 +2417,79 @@
       </c>
       <c r="H14">
         <f>H8+H10+H11+H12</f>
-        <v>751747.0</v>
+        <v>633605.0</v>
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>807644.0</v>
+        <v>680575.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>866020.0</v>
+        <v>729236.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>927011.0</v>
+        <v>779791.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>990793.0</v>
+        <v>832371.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>1057636.0</v>
+        <v>887135.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>1127728.0</v>
+        <v>944252.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>1201351.0</v>
+        <v>1003943.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>1278738.0</v>
+        <v>1066307.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>1360233.0</v>
+        <v>1131611.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>1446099.0</v>
+        <v>1200090.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>1536617.0</v>
+        <v>1271890.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>1632217.0</v>
+        <v>1347349.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>1733357.0</v>
+        <v>1426765.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>1840334.0</v>
+        <v>1510444.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>1953587.0</v>
+        <v>1598593.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>2073645.0</v>
+        <v>1691635.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>2201018.0</v>
+        <v>1789947.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>2336320.0</v>
+        <v>1894009.0</v>
       </c>
     </row>
   </sheetData>
@@ -2650,83 +2649,83 @@
       </c>
       <c r="H5">
         <f>Revenue!H15</f>
-        <v>1279484.0</v>
+        <v>919953.0</v>
       </c>
       <c r="I5">
         <f>Revenue!I15</f>
-        <v>1376777.0</v>
+        <v>990079.0</v>
       </c>
       <c r="J5">
         <f>Revenue!J15</f>
-        <v>1481615.0</v>
+        <v>1065354.0</v>
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>1594411.0</v>
+        <v>1146390.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>1715704.0</v>
+        <v>1233592.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>1846305.0</v>
+        <v>1327432.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>1986794.0</v>
+        <v>1428436.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>2138029.0</v>
+        <v>1537274.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>2300714.0</v>
+        <v>1654244.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>2475903.0</v>
+        <v>1780158.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>2664389.0</v>
+        <v>1915732.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>2867038.0</v>
+        <v>2061416.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>3085144.0</v>
+        <v>2218232.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>3320115.0</v>
+        <v>2387089.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>3572849.0</v>
+        <v>2568923.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>3844677.0</v>
+        <v>2764354.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>4137216.0</v>
+        <v>2974675.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>4452012.0</v>
+        <v>3201034.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>4790936.0</v>
+        <v>3444891.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>56091833.0</v>
+        <v>41780979.0</v>
       </c>
     </row>
     <row r="6">
@@ -2757,83 +2756,83 @@
       </c>
       <c r="H6">
         <f>-Costs!H10</f>
-        <v>-286732.0</v>
+        <v>-206161.0</v>
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-308536.0</v>
+        <v>-221877.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-332030.0</v>
+        <v>-238746.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-357308.0</v>
+        <v>-256906.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-384489.0</v>
+        <v>-276448.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-413757.0</v>
+        <v>-297478.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-445241.0</v>
+        <v>-320113.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-479132.0</v>
+        <v>-344503.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-515590.0</v>
+        <v>-370716.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-554850.0</v>
+        <v>-398933.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-597090.0</v>
+        <v>-429316.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-642503.0</v>
+        <v>-461963.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-691381.0</v>
+        <v>-497106.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-744038.0</v>
+        <v>-534947.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-800675.0</v>
+        <v>-575696.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-861592.0</v>
+        <v>-619492.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-927150.0</v>
+        <v>-666625.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-997696.0</v>
+        <v>-717352.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-1073649.0</v>
+        <v>-772000.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-12570182.0</v>
+        <v>-9363121.0</v>
       </c>
     </row>
     <row r="7">
@@ -2864,83 +2863,83 @@
       </c>
       <c r="H7">
         <f>H5+H6</f>
-        <v>992752.0</v>
+        <v>713792.0</v>
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>1068241.0</v>
+        <v>768202.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>1149585.0</v>
+        <v>826608.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>1237103.0</v>
+        <v>889484.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>1331215.0</v>
+        <v>957144.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>1432548.0</v>
+        <v>1029954.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>1541553.0</v>
+        <v>1108323.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>1658897.0</v>
+        <v>1192771.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>1785124.0</v>
+        <v>1283528.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>1921053.0</v>
+        <v>1381225.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>2067299.0</v>
+        <v>1486416.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>2224535.0</v>
+        <v>1599453.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>2393763.0</v>
+        <v>1721126.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>2576077.0</v>
+        <v>1852142.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>2772174.0</v>
+        <v>1993227.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>2983085.0</v>
+        <v>2144862.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>3210066.0</v>
+        <v>2308050.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>3454316.0</v>
+        <v>2483682.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>3717287.0</v>
+        <v>2672891.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>43521651.0</v>
+        <v>32417858.0</v>
       </c>
     </row>
     <row r="8">
@@ -3181,83 +3180,83 @@
       </c>
       <c r="H11">
         <f>-Costs!H11</f>
-        <v>-133706.0</v>
+        <v>-96135.0</v>
       </c>
       <c r="I11">
         <f>-Costs!I11</f>
-        <v>-143873.0</v>
+        <v>-103463.0</v>
       </c>
       <c r="J11">
         <f>-Costs!J11</f>
-        <v>-154829.0</v>
+        <v>-111329.0</v>
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-166616.0</v>
+        <v>-119798.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-179291.0</v>
+        <v>-128910.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-192939.0</v>
+        <v>-138717.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-207620.0</v>
+        <v>-149272.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-223424.0</v>
+        <v>-160645.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-240425.0</v>
+        <v>-172868.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-258732.0</v>
+        <v>-186027.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-278429.0</v>
+        <v>-200194.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-299605.0</v>
+        <v>-215418.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-322398.0</v>
+        <v>-231805.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-346952.0</v>
+        <v>-249451.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-373363.0</v>
+        <v>-268452.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-401769.0</v>
+        <v>-288875.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-432339.0</v>
+        <v>-310854.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-465235.0</v>
+        <v>-334508.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-500653.0</v>
+        <v>-359991.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-5861597.0</v>
+        <v>-4366111.0</v>
       </c>
     </row>
     <row r="12">
@@ -3395,83 +3394,83 @@
       </c>
       <c r="H13">
         <f>H10+H11+H12</f>
-        <v>-465015.0</v>
+        <v>-427444.0</v>
       </c>
       <c r="I13">
         <f>I10+I11+I12</f>
-        <v>-499108.0</v>
+        <v>-458698.0</v>
       </c>
       <c r="J13">
         <f>J10+J11+J12</f>
-        <v>-533990.0</v>
+        <v>-490490.0</v>
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-569703.0</v>
+        <v>-522885.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-606304.0</v>
+        <v>-555923.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-643879.0</v>
+        <v>-589657.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-682487.0</v>
+        <v>-624139.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-722219.0</v>
+        <v>-659440.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-763148.0</v>
+        <v>-695591.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-805383.0</v>
+        <v>-732678.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-849009.0</v>
+        <v>-770774.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-894114.0</v>
+        <v>-809927.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-940836.0</v>
+        <v>-850243.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-989319.0</v>
+        <v>-891818.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-1039659.0</v>
+        <v>-934748.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-1091995.0</v>
+        <v>-979101.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-1146495.0</v>
+        <v>-1025010.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-1203322.0</v>
+        <v>-1072595.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-1262671.0</v>
+        <v>-1122009.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-17545720.0</v>
+        <v>-16050234.0</v>
       </c>
     </row>
     <row r="15">
@@ -3502,83 +3501,83 @@
       </c>
       <c r="H15">
         <f>H7+H13</f>
-        <v>527737.0</v>
+        <v>286348.0</v>
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>569133.0</v>
+        <v>309504.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>615595.0</v>
+        <v>336118.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>667400.0</v>
+        <v>366599.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>724911.0</v>
+        <v>401221.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>788669.0</v>
+        <v>440297.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>859066.0</v>
+        <v>484184.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>936678.0</v>
+        <v>533331.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>1021976.0</v>
+        <v>587937.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>1115670.0</v>
+        <v>648547.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>1218290.0</v>
+        <v>715642.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>1330421.0</v>
+        <v>789526.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>1452927.0</v>
+        <v>870883.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>1586758.0</v>
+        <v>960324.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>1732515.0</v>
+        <v>1058479.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>1891090.0</v>
+        <v>1165761.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>2063571.0</v>
+        <v>1283040.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>2250994.0</v>
+        <v>1411087.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>2454616.0</v>
+        <v>1550882.0</v>
       </c>
       <c r="AA15">
-        <f>SUM(C15:Z15)</f>
-        <v>25975931.0</v>
+        <f>SUM(C15:Y15)</f>
+        <v>14816742.0</v>
       </c>
     </row>
     <row r="16">
@@ -3609,79 +3608,79 @@
       </c>
       <c r="H16">
         <f>IF(H5=0,0,ROUND(H15/H5,4))</f>
-        <v>0.4125</v>
+        <v>0.3113</v>
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.4134</v>
+        <v>0.3126</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.4155</v>
+        <v>0.3155</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.4186</v>
+        <v>0.3198</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.4225</v>
+        <v>0.3252</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.4272</v>
+        <v>0.3317</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.4324</v>
+        <v>0.339</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.4381</v>
+        <v>0.3469</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.4442</v>
+        <v>0.3554</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.4506</v>
+        <v>0.3643</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.4572</v>
+        <v>0.3736</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.464</v>
+        <v>0.383</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.4709</v>
+        <v>0.3926</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.4779</v>
+        <v>0.4023</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.4849</v>
+        <v>0.412</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.4919</v>
+        <v>0.4217</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.4988</v>
+        <v>0.4313</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.5056</v>
+        <v>0.4408</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.5123</v>
+        <v>0.4502</v>
       </c>
     </row>
     <row r="18">
@@ -3712,79 +3711,79 @@
       </c>
       <c r="H18">
         <f>G18+H15</f>
-        <v>2695651.0</v>
+        <v>2454262.0</v>
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>3264784.0</v>
+        <v>2763766.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>3880379.0</v>
+        <v>3099884.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>4547779.0</v>
+        <v>3466483.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>5272690.0</v>
+        <v>3867704.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>6061359.0</v>
+        <v>4308001.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>6920425.0</v>
+        <v>4792185.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>7857103.0</v>
+        <v>5325516.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>8879079.0</v>
+        <v>5913453.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>9994749.0</v>
+        <v>6562000.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>11213039.0</v>
+        <v>7277642.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>12543460.0</v>
+        <v>8067168.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>13996387.0</v>
+        <v>8938051.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>15583145.0</v>
+        <v>9898375.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>17315660.0</v>
+        <v>10956854.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>19206750.0</v>
+        <v>12122615.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>21270321.0</v>
+        <v>13405655.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>23521315.0</v>
+        <v>14816742.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>25975931.0</v>
+        <v>16367624.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3815,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>56091833.0</v>
+        <v>41780979.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3826,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>25975931.0</v>
+        <v>14816742.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3837,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>19055506.0</v>
+        <v>11575439.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3859,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>236288274.0</v>
+        <v>143535444.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3881,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>231438274.0</v>
+        <v>138685444.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>1082330.4583333333</v>
+        <v>681984.3333333334</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3903,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>2454616.0</v>
+        <v>1550882.0</v>
       </c>
     </row>
     <row r="13">
@@ -3915,7 +3914,7 @@
       </c>
       <c r="B13">
         <f>MIN('P&amp;L'!C15:Z15)</f>
-        <v>383627.0</v>
+        <v>286348.0</v>
       </c>
     </row>
     <row r="14">
@@ -3926,7 +3925,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>25975931.0</v>
+        <v>16367624.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3936,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>2070989.0</v>
+        <v>1264534.0</v>
       </c>
     </row>
   </sheetData>
